--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487726_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487726_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8469</v>
+        <v>4.2341</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5281</v>
+        <v>5.8879</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6811</v>
+        <v>-1.6539</v>
       </c>
       <c r="G2" t="n">
         <v>2.7212</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0675</v>
+        <v>-0.5454</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5473</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4798</v>
+        <v>-0.4525</v>
       </c>
       <c r="V2" t="n">
         <v>0.894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9171</v>
+        <v>2.4355</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9742</v>
+        <v>2.8741</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0571</v>
+        <v>-0.4387</v>
       </c>
       <c r="G3" t="n">
         <v>0.526</v>
@@ -688,13 +688,13 @@
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2732</v>
+        <v>0.7915</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6202</v>
+        <v>0.5201</v>
       </c>
       <c r="U3" t="n">
-        <v>0.653</v>
+        <v>0.2714</v>
       </c>
       <c r="V3" t="n">
         <v>1.506</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7569</v>
+        <v>1.7842</v>
       </c>
       <c r="E4" t="n">
         <v>1.8073</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0504</v>
+        <v>-0.0231</v>
       </c>
       <c r="G4" t="n">
         <v>0.477</v>
@@ -766,13 +766,13 @@
         <v>3.1045</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4664</v>
+        <v>-0.4391</v>
       </c>
       <c r="T4" t="n">
         <v>-0.4229</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0435</v>
+        <v>-0.0162</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0959</v>
+        <v>-0.8894</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8947</v>
+        <v>-1.4618</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9905</v>
+        <v>0.5724</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.7482</v>
+        <v>-2.2992</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1411</v>
+        <v>-1.2259</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6072</v>
+        <v>-1.0733</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.2121</v>
+        <v>-1.5571</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2101</v>
+        <v>-0.2224</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.002</v>
+        <v>-1.3347</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5362</v>
+        <v>-0.7421</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.931</v>
+        <v>-1.0035</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3948</v>
+        <v>0.2614</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R5" t="n">
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>2.262</v>
+        <v>0.0516</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2875</v>
+        <v>0.0073</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9745</v>
+        <v>0.0443</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5778</v>
+        <v>-1.1048</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1229</v>
+        <v>-2.7956</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5451</v>
+        <v>1.6907</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2992</v>
+        <v>-2.7482</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2259</v>
+        <v>-1.1411</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0733</v>
+        <v>-1.6072</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5571</v>
+        <v>-2.2121</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2224</v>
+        <v>-0.2101</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3347</v>
+        <v>-2.002</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7421</v>
+        <v>-0.5362</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0035</v>
+        <v>-0.931</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2614</v>
+        <v>0.3948</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
         <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6368</v>
+        <v>1.0613</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6539</v>
+        <v>0.3866</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0171</v>
+        <v>0.6747</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3939</v>
+        <v>-1.7878</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.559</v>
+        <v>-1.1981</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8349</v>
+        <v>-0.5897</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0412</v>
@@ -1000,13 +1000,13 @@
         <v>2.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3692</v>
+        <v>0.2369</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1683</v>
+        <v>0.1926</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.201</v>
+        <v>0.0443</v>
       </c>
       <c r="V7" t="n">
         <v>-2.7298</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.455</v>
+        <v>-2.7607</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.533</v>
+        <v>-0.9106</v>
       </c>
       <c r="F8" t="n">
-        <v>0.078</v>
+        <v>-1.8501</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6613</v>
+        <v>-3.5223</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1765</v>
+        <v>-2.4378</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4848</v>
+        <v>-1.0844</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.379</v>
+        <v>-1.1905</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2884</v>
+        <v>-1.1905</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2824</v>
+        <v>-2.3318</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4649</v>
+        <v>-1.2473</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8175</v>
+        <v>-1.0844</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7164</v>
+        <v>0.5821</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5944</v>
+        <v>-0.1026</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6684</v>
+        <v>-0.2843</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.074</v>
+        <v>0.1817</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2821</v>
+        <v>0.5642</v>
       </c>
       <c r="X8" t="n">
         <v>-0.2821</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0699</v>
+        <v>-2.9672</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1108</v>
+        <v>-2.7727</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9591</v>
+        <v>-0.1945</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5223</v>
+        <v>-2.6613</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4378</v>
+        <v>-1.1765</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0844</v>
+        <v>-1.4848</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1905</v>
+        <v>-0.379</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1905</v>
+        <v>0.2884</v>
       </c>
       <c r="L9" t="n">
+        <v>-0.6673</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-2.2824</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1.4649</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.8175</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.3881</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-3.1045</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.7164</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.3465</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>-2.3318</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-1.2473</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-1.0844</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.5821</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.5821</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.4118</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.4845</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.0727</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>0.2821</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.5642</v>
       </c>
       <c r="X9" t="n">
         <v>-0.2821</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2077</v>
+        <v>-3.562</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0531</v>
+        <v>-2.6527</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1546</v>
+        <v>-0.9093</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6373</v>
@@ -1234,13 +1234,13 @@
         <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9883</v>
+        <v>-0.3426</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4116</v>
+        <v>-0.0112</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5767</v>
+        <v>-0.3314</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7614</v>
+        <v>-5.8277</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.0946</v>
+        <v>-6.4334</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3331</v>
+        <v>0.6057</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2131</v>
@@ -1312,13 +1312,13 @@
         <v>4.2687</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4424</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7863</v>
+        <v>-0.1251</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6561</v>
+        <v>-0.3835</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9418</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.8489</v>
+        <v>-10.4458</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.0585</v>
+        <v>-7.6556</v>
       </c>
       <c r="F12" t="n">
         <v>-2.7905</v>
@@ -1390,13 +1390,13 @@
         <v>22.3137</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1177999999999995</v>
+        <v>0.2851</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1958999999999997</v>
+        <v>0.5990000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3138</v>
+        <v>-0.3137</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2134</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7826</v>
+        <v>5.1181</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5516</v>
+        <v>1.7508</v>
       </c>
       <c r="F13" t="n">
-        <v>3.231</v>
+        <v>3.3673</v>
       </c>
       <c r="G13" t="n">
         <v>1.385</v>
@@ -1468,13 +1468,13 @@
         <v>2.5224</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0558</v>
+        <v>1.3913</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5298</v>
+        <v>0.729</v>
       </c>
       <c r="U13" t="n">
-        <v>0.526</v>
+        <v>0.6623</v>
       </c>
       <c r="V13" t="n">
         <v>2.7298</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.857</v>
+        <v>4.659</v>
       </c>
       <c r="E14" t="n">
-        <v>4.303</v>
+        <v>3.2816</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5541</v>
+        <v>1.3775</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9662</v>
+        <v>1.8526</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4408</v>
+        <v>0.8955</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5254</v>
+        <v>0.9571</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9629</v>
+        <v>2.0207</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3718</v>
+        <v>1.3306</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6901</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0033</v>
+        <v>-0.1681</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.931</v>
+        <v>-0.435</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9343</v>
+        <v>0.2669</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1938</v>
+        <v>0.4183</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8625</v>
+        <v>0.037</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6687</v>
+        <v>0.3813</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9209</v>
+        <v>1.2239</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4477</v>
+        <v>1.2239</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1797</v>
+        <v>4.3265</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8812</v>
+        <v>3.8025</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2985</v>
+        <v>0.524</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8526</v>
+        <v>1.9662</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8955</v>
+        <v>0.4408</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9571</v>
+        <v>1.5254</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0207</v>
+        <v>1.9629</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3306</v>
+        <v>1.3718</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6901</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1681</v>
+        <v>0.0033</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.435</v>
+        <v>-0.931</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2669</v>
+        <v>0.9343</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.061</v>
+        <v>-0.3367</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3634</v>
+        <v>0.362</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3024</v>
+        <v>-0.6987</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2239</v>
+        <v>1.9209</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>2.4477</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5269</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5984</v>
+        <v>2.9898</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5129</v>
+        <v>1.0134</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0855</v>
+        <v>1.9765</v>
       </c>
       <c r="G16" t="n">
         <v>7.9385</v>
@@ -1702,13 +1702,13 @@
         <v>2.3284</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.2038</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7268</v>
+        <v>-0.2263</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1315</v>
+        <v>0.0225</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2821</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4418</v>
+        <v>0.9385</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4628</v>
+        <v>-0.898</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9046</v>
+        <v>1.8365</v>
       </c>
       <c r="G17" t="n">
-        <v>2.936</v>
+        <v>-0.331</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.1046</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7994</v>
+        <v>-0.2263</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3562</v>
+        <v>-0.1777</v>
       </c>
       <c r="K17" t="n">
-        <v>0.758</v>
+        <v>1.1164</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5982</v>
+        <v>-1.2941</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4202</v>
+        <v>-0.1533</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6214</v>
+        <v>-1.221</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2012</v>
+        <v>1.0677</v>
       </c>
       <c r="P17" t="n">
+        <v>1.1642</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0554</v>
+        <v>-0.5067</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9085</v>
+        <v>-0.0323</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8531</v>
+        <v>-0.4744</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4686</v>
+        <v>0.6119</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4686</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.885</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3985</v>
+        <v>0.0377</v>
       </c>
       <c r="F18" t="n">
-        <v>1.485</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.331</v>
+        <v>2.936</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1046</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2263</v>
+        <v>3.7994</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1777</v>
+        <v>3.3562</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1164</v>
+        <v>0.758</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2941</v>
+        <v>2.5982</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1533</v>
+        <v>-0.4202</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.221</v>
+        <v>-1.6214</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0677</v>
+        <v>1.2012</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3587</v>
+        <v>0.3878</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.408</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8259</v>
+        <v>0.7958</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6119</v>
+        <v>-1.4686</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3299</v>
+        <v>-1.4686</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8949</v>
+        <v>-0.7896</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4152</v>
+        <v>-2.0584</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5204</v>
+        <v>1.2688</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8042</v>
+        <v>-1.4416</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8603</v>
+        <v>-2.2129</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0561</v>
+        <v>0.7713</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-0.7198</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0133</v>
+        <v>-0.1565</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1218</v>
+        <v>-0.5633</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0873</v>
+        <v>-0.7217</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8469</v>
+        <v>-2.0564</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9343</v>
+        <v>1.3347</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>2.5224</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6557</v>
+        <v>-0.3735</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1047</v>
+        <v>-0.3685</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5508999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="V19" t="n">
+        <v>-0.5269</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="W19" t="n">
-        <v>0.2821</v>
-      </c>
       <c r="X19" t="n">
-        <v>-0.2821</v>
+        <v>-0.5269</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3051</v>
+        <v>-1.6144</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2936</v>
+        <v>1.0934</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5987</v>
+        <v>-2.7078</v>
       </c>
       <c r="G20" t="n">
         <v>1.8378</v>
@@ -2014,13 +2014,13 @@
         <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.316</v>
+        <v>-0.6253</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1828</v>
+        <v>-0.0174</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4988</v>
+        <v>-0.6079</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4686</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5265</v>
+        <v>-1.6684</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.659</v>
+        <v>-3.216</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1325</v>
+        <v>1.5476</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4416</v>
+        <v>-0.8042</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2129</v>
+        <v>-1.8603</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7713</v>
+        <v>1.0561</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7198</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1565</v>
+        <v>-1.0133</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5633</v>
+        <v>0.1218</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7217</v>
+        <v>0.0873</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0564</v>
+        <v>-0.8469</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3347</v>
+        <v>0.9343</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5523</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5224</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1103</v>
+        <v>0.8821</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9691</v>
+        <v>0.3039</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1413</v>
+        <v>0.5782</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5269</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5269</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3705</v>
+        <v>-3.3282</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.04</v>
+        <v>-3.2402</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3305</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-2.941</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2907</v>
+        <v>-0.2484</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1346</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4253</v>
+        <v>-0.1828</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5269</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.849</v>
+        <v>11.5163</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5668</v>
+        <v>1.566799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>9.282399999999999</v>
+        <v>9.949700000000002</v>
       </c>
       <c r="G23" t="n">
         <v>12.3983</v>
@@ -2248,22 +2248,22 @@
         <v>18.4331</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1178999999999998</v>
+        <v>0.7851000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3138000000000001</v>
+        <v>0.3137999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1961</v>
+        <v>0.4713000000000002</v>
       </c>
       <c r="V23" t="n">
         <v>2.2134</v>
       </c>
       <c r="W23" t="n">
-        <v>9.083500000000001</v>
+        <v>9.083499999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.870200000000001</v>
+        <v>-6.8702</v>
       </c>
     </row>
   </sheetData>
